--- a/src/utils/sxsyzlzq/shijiesai/all4_count.xlsx
+++ b/src/utils/sxsyzlzq/shijiesai/all4_count.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="137">
   <si>
     <t>区服+名字</t>
   </si>
@@ -58,309 +58,336 @@
     <t>总数</t>
   </si>
   <si>
+    <t>129-WZ(旧城之下)</t>
+  </si>
+  <si>
+    <t>129-亚麻</t>
+  </si>
+  <si>
+    <t>130-随￥缘</t>
+  </si>
+  <si>
+    <t>130-自然</t>
+  </si>
+  <si>
+    <t>131-朝闻道</t>
+  </si>
+  <si>
+    <t>131-孔琦</t>
+  </si>
+  <si>
+    <t>131-神经蛙</t>
+  </si>
+  <si>
+    <t>132-YOKE</t>
+  </si>
+  <si>
+    <t>133-抹小布</t>
+  </si>
+  <si>
+    <t>133-神经蛙</t>
+  </si>
+  <si>
+    <t>133-杨豆豆</t>
+  </si>
+  <si>
+    <t>133-叶小怪</t>
+  </si>
+  <si>
+    <t>133-政杨</t>
+  </si>
+  <si>
+    <t>134-高戈</t>
+  </si>
+  <si>
+    <t>134-木轩</t>
+  </si>
+  <si>
+    <t>134-跑</t>
+  </si>
+  <si>
+    <t>134-破灭</t>
+  </si>
+  <si>
+    <t>135-常世万法仙君</t>
+  </si>
+  <si>
+    <t>135-卡洛</t>
+  </si>
+  <si>
+    <t>135-唔昂 王</t>
+  </si>
+  <si>
+    <t>135-真理铁拳</t>
+  </si>
+  <si>
+    <t>136-0.o</t>
+  </si>
+  <si>
+    <t>136-miko</t>
+  </si>
+  <si>
+    <t>136-OK（开尔文</t>
+  </si>
+  <si>
+    <t>136-标</t>
+  </si>
+  <si>
+    <t>136-神经蛙</t>
+  </si>
+  <si>
+    <t>136-植物园园长</t>
+  </si>
+  <si>
+    <t>137-No1.Mr</t>
+  </si>
+  <si>
+    <t>137-vwafew</t>
+  </si>
+  <si>
+    <t>137-菜的够吊</t>
+  </si>
+  <si>
+    <t>137-神之千手(神之一手)</t>
+  </si>
+  <si>
+    <t>137-神之右手</t>
+  </si>
+  <si>
+    <t>137-随便玩玩</t>
+  </si>
+  <si>
+    <t>137-王熠</t>
+  </si>
+  <si>
+    <t>137-未雨</t>
+  </si>
+  <si>
+    <t>137-星星</t>
+  </si>
+  <si>
+    <t>137-鹰の一手</t>
+  </si>
+  <si>
+    <t>138-LEO</t>
+  </si>
+  <si>
+    <t>139-Lyric</t>
+  </si>
+  <si>
+    <t>139-Sure</t>
+  </si>
+  <si>
+    <t>139-加禾影像|阿</t>
+  </si>
+  <si>
+    <t>139-蒋凌峰</t>
+  </si>
+  <si>
+    <t>141-黑色香槟</t>
+  </si>
+  <si>
+    <t>142-Limere</t>
+  </si>
+  <si>
+    <t>142-多幸运</t>
+  </si>
+  <si>
+    <t>142-老猫</t>
+  </si>
+  <si>
+    <t>142-异界淘金者</t>
+  </si>
+  <si>
+    <t>144-zwy(九霄环佩)</t>
+  </si>
+  <si>
+    <t>144-草莓硬糖</t>
+  </si>
+  <si>
+    <t>144-神经蛙</t>
+  </si>
+  <si>
+    <t>144-烟雨平生</t>
+  </si>
+  <si>
+    <t>145-[永恒]</t>
+  </si>
+  <si>
+    <t>145-1</t>
+  </si>
+  <si>
+    <t>145-杜佳捷</t>
+  </si>
+  <si>
+    <t>145-SZH(老王)</t>
+  </si>
+  <si>
+    <t>145-古月星辰</t>
+  </si>
+  <si>
+    <t>145-九龙亦云</t>
+  </si>
+  <si>
+    <t>145-明</t>
+  </si>
+  <si>
+    <t>145-清风</t>
+  </si>
+  <si>
+    <t>145-小黑</t>
+  </si>
+  <si>
+    <t>145-夜的第七z</t>
+  </si>
+  <si>
+    <t>146-KB</t>
+  </si>
+  <si>
+    <t>146-Thor</t>
+  </si>
+  <si>
+    <t>146-江南</t>
+  </si>
+  <si>
+    <t>146-谢之求学者(念苍生)</t>
+  </si>
+  <si>
+    <t>147-没有nic</t>
+  </si>
+  <si>
+    <t>148-12345</t>
+  </si>
+  <si>
+    <t>148-白夜</t>
+  </si>
+  <si>
+    <t>148-大锅</t>
+  </si>
+  <si>
+    <t>148-大核桃</t>
+  </si>
+  <si>
+    <t>148-momo</t>
+  </si>
+  <si>
+    <t>148-攀攀</t>
+  </si>
+  <si>
+    <t>148-请叫我阿奎</t>
+  </si>
+  <si>
+    <t>148-水煮肉片(数字经济)</t>
+  </si>
+  <si>
+    <t>148-淘汰郎</t>
+  </si>
+  <si>
+    <t>148-玩玩</t>
+  </si>
+  <si>
+    <t>149-灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>149-柒柒</t>
+  </si>
+  <si>
+    <t>150-开飞机的贝塔</t>
+  </si>
+  <si>
+    <t>150-夏进</t>
+  </si>
+  <si>
+    <t>150-朱</t>
+  </si>
+  <si>
+    <t>151-suola</t>
+  </si>
+  <si>
+    <t>151-星空</t>
+  </si>
+  <si>
+    <t>152-养乐多</t>
+  </si>
+  <si>
+    <t>154-。马铃薯</t>
+  </si>
+  <si>
+    <t>154-Felix</t>
+  </si>
+  <si>
+    <t>154-吃鹿的于</t>
+  </si>
+  <si>
+    <t>154-江江江</t>
+  </si>
+  <si>
+    <t>155-锋云</t>
+  </si>
+  <si>
+    <t>156-Tiao跳猪</t>
+  </si>
+  <si>
+    <t>157-#</t>
+  </si>
+  <si>
+    <t>157-动次打次</t>
+  </si>
+  <si>
     <t>157-段</t>
   </si>
   <si>
-    <t>129-WZ(旧城之下)</t>
-  </si>
-  <si>
-    <t>146-KB</t>
-  </si>
-  <si>
-    <t>159-神瑛</t>
-  </si>
-  <si>
-    <t>144-zwy(九霄环佩)</t>
-  </si>
-  <si>
-    <t>149-灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>146-江南</t>
-  </si>
-  <si>
-    <t>137-No1.Mr</t>
-  </si>
-  <si>
-    <t>148-大核桃</t>
-  </si>
-  <si>
-    <t>151-星空</t>
-  </si>
-  <si>
-    <t>145-古希腊掌管贫穷(Mr.Go)</t>
-  </si>
-  <si>
-    <t>148-请叫我阿奎</t>
-  </si>
-  <si>
-    <t>156-Tiao跳猪</t>
-  </si>
-  <si>
-    <t>150-开飞机的贝塔</t>
-  </si>
-  <si>
-    <t>157-#</t>
-  </si>
-  <si>
-    <t>137-鹰の一手</t>
-  </si>
-  <si>
-    <t>154-吃鹿的于</t>
-  </si>
-  <si>
-    <t>130-随￥缘</t>
-  </si>
-  <si>
-    <t>145-杜佳捷</t>
-  </si>
-  <si>
-    <t>134-木轩</t>
-  </si>
-  <si>
-    <t>137-神之千手(神之一手)</t>
-  </si>
-  <si>
-    <t>145-古月星辰</t>
+    <t>157-寡王</t>
   </si>
   <si>
     <t>157-空泣</t>
   </si>
   <si>
-    <t>148-水煮肉片(数字经济)</t>
-  </si>
-  <si>
-    <t>142-异界淘金者</t>
-  </si>
-  <si>
-    <t>154-。马铃薯</t>
-  </si>
-  <si>
-    <t>131-孔琦</t>
-  </si>
-  <si>
-    <t>133-叶小怪</t>
-  </si>
-  <si>
-    <t>151-suola</t>
-  </si>
-  <si>
-    <t>145-小黑</t>
-  </si>
-  <si>
-    <t>136-标</t>
-  </si>
-  <si>
-    <t>131-神经蛙</t>
-  </si>
-  <si>
-    <t>142-Limere</t>
-  </si>
-  <si>
-    <t>145-1</t>
-  </si>
-  <si>
-    <t>133-抹小布</t>
-  </si>
-  <si>
-    <t>136-miko</t>
-  </si>
-  <si>
-    <t>141-黑色香槟</t>
-  </si>
-  <si>
-    <t>148-12345</t>
-  </si>
-  <si>
-    <t>137-未雨</t>
-  </si>
-  <si>
-    <t>134-跑</t>
-  </si>
-  <si>
-    <t>136-植物园园长</t>
-  </si>
-  <si>
-    <t>137-王熠</t>
-  </si>
-  <si>
-    <t>139-Lyric</t>
-  </si>
-  <si>
-    <t>147-没有nic</t>
-  </si>
-  <si>
-    <t>148-淘汰郎</t>
+    <t>157-神经蛙</t>
+  </si>
+  <si>
+    <t>157-躺平的蛙</t>
+  </si>
+  <si>
+    <t>157-我姓孟.</t>
   </si>
   <si>
     <t>158-nn</t>
   </si>
   <si>
+    <t>159-Jason（神樱）</t>
+  </si>
+  <si>
+    <t>159-叶随清风</t>
+  </si>
+  <si>
     <t>160-sky</t>
   </si>
   <si>
-    <t>133-杨豆豆</t>
-  </si>
-  <si>
-    <t>139-Sure</t>
-  </si>
-  <si>
-    <t>145-[永恒]</t>
-  </si>
-  <si>
-    <t>142-多幸运</t>
-  </si>
-  <si>
-    <t>152-养乐多</t>
-  </si>
-  <si>
-    <t>130-自然</t>
-  </si>
-  <si>
-    <t>132-YOKE</t>
-  </si>
-  <si>
-    <t>135-卡洛</t>
-  </si>
-  <si>
-    <t>135-唔昂 王</t>
-  </si>
-  <si>
-    <t>136-0.o</t>
-  </si>
-  <si>
-    <t>137-菜的够吊</t>
-  </si>
-  <si>
-    <t>138-LEO</t>
-  </si>
-  <si>
-    <t>145-明</t>
-  </si>
-  <si>
-    <t>145-夜的第七z</t>
-  </si>
-  <si>
-    <t>146-谢之求学者(念苍生)</t>
-  </si>
-  <si>
-    <t>150-朱</t>
-  </si>
-  <si>
-    <t>157-躺平的蛙</t>
-  </si>
-  <si>
-    <t>131-朝闻道</t>
-  </si>
-  <si>
-    <t>133-神经蛙</t>
-  </si>
-  <si>
-    <t>133-政杨</t>
-  </si>
-  <si>
-    <t>134-高戈</t>
-  </si>
-  <si>
-    <t>134-破灭</t>
-  </si>
-  <si>
-    <t>135-常世万法仙君</t>
-  </si>
-  <si>
-    <t>135-真理铁拳</t>
-  </si>
-  <si>
-    <t>136-OK（开尔文</t>
-  </si>
-  <si>
-    <t>136-神经蛙</t>
-  </si>
-  <si>
-    <t>137-vwafew</t>
-  </si>
-  <si>
-    <t>137-神之右手</t>
-  </si>
-  <si>
-    <t>137-随便玩玩</t>
-  </si>
-  <si>
-    <t>137-星星</t>
-  </si>
-  <si>
-    <t>139-加禾影像|阿</t>
-  </si>
-  <si>
-    <t>139-蒋凌峰</t>
-  </si>
-  <si>
-    <t>142-老猫</t>
-  </si>
-  <si>
-    <t>144-神经蛙</t>
-  </si>
-  <si>
-    <t>145-九龙亦云</t>
-  </si>
-  <si>
-    <t>145-清风</t>
-  </si>
-  <si>
-    <t>146-Thor</t>
-  </si>
-  <si>
-    <t>148-白夜</t>
-  </si>
-  <si>
-    <t>148-大锅</t>
-  </si>
-  <si>
-    <t>148-玩玩</t>
-  </si>
-  <si>
-    <t>149-柒柒</t>
-  </si>
-  <si>
-    <t>150-夏进</t>
-  </si>
-  <si>
-    <t>154-Felix</t>
-  </si>
-  <si>
-    <t>155-锋云</t>
-  </si>
-  <si>
-    <t>157-动次打次</t>
-  </si>
-  <si>
-    <t>157-寡王</t>
-  </si>
-  <si>
-    <t>157-神经蛙</t>
-  </si>
-  <si>
-    <t>157-我姓孟.</t>
-  </si>
-  <si>
-    <t>159-叶随清风</t>
-  </si>
-  <si>
     <t>总数：</t>
   </si>
   <si>
+    <t>第十一届</t>
+  </si>
+  <si>
+    <t>旧城之下</t>
+  </si>
+  <si>
+    <t>企鹅</t>
+  </si>
+  <si>
+    <t>zwy</t>
+  </si>
+  <si>
+    <t>神经蛙</t>
+  </si>
+  <si>
     <t>第九届</t>
   </si>
   <si>
-    <t>旧城之下</t>
-  </si>
-  <si>
     <t>段</t>
   </si>
   <si>
-    <t>企鹅</t>
-  </si>
-  <si>
     <t>阿奎</t>
   </si>
   <si>
@@ -404,9 +431,6 @@
   </si>
   <si>
     <t>第三届</t>
-  </si>
-  <si>
-    <t>zwy</t>
   </si>
   <si>
     <t>第二届</t>
@@ -1357,7 +1381,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1401,272 +1425,194 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I65" si="0">SUM(B2:H2)</f>
-        <v>9</v>
+        <f>SUM(B2:H2)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>SUM(B3:H3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B4:H4)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B5:H5)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
       <c r="G6">
         <v>1</v>
       </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
       <c r="I6">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B6:H6)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
         <v>3</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
       <c r="I7">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B7:H7)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="H8">
+      <c r="G8">
         <v>2</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B8:H8)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9">
+      <c r="H9">
         <v>2</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B9:H9)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>SUM(B10:H10)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
+      <c r="E11">
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B11:H11)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>3</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
       <c r="H12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>SUM(B12:H12)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
       <c r="G13">
         <v>4</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B13:H13)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
       <c r="H14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B14:H14)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B15:H15)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1674,143 +1620,107 @@
         <v>23</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>SUM(B16:H16)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>24</v>
       </c>
-      <c r="F17">
-        <v>3</v>
-      </c>
       <c r="G17">
-        <v>2</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B17:H17)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>25</v>
       </c>
-      <c r="F18">
-        <v>2</v>
+      <c r="H18">
+        <v>1</v>
       </c>
       <c r="I18">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B18:H18)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>4</v>
+      <c r="H19">
+        <v>1</v>
       </c>
       <c r="I19">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B19:H19)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
       <c r="H20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B20:H20)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
       <c r="H21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B21:H21)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B22:H22)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
       <c r="H23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B23:H23)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
       <c r="G24">
         <v>1</v>
       </c>
@@ -1818,53 +1728,47 @@
         <v>2</v>
       </c>
       <c r="I24">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B24:H24)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
+      <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B25:H25)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="F26">
-        <v>1</v>
+      <c r="G26">
+        <v>2</v>
       </c>
       <c r="H26">
         <v>2</v>
       </c>
       <c r="I26">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B26:H26)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>34</v>
       </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B27:H27)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1872,65 +1776,65 @@
         <v>35</v>
       </c>
       <c r="G28">
-        <v>4</v>
-      </c>
-      <c r="H28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B28:H28)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
         <v>36</v>
       </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
       <c r="G29">
-        <v>4</v>
-      </c>
-      <c r="H29">
         <v>2</v>
       </c>
       <c r="I29">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B29:H29)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="G30">
-        <v>3</v>
-      </c>
       <c r="H30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B30:H30)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
         <v>38</v>
       </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
       <c r="H31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>SUM(B31:H31)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
         <v>39</v>
       </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
       <c r="G32">
         <v>2</v>
       </c>
@@ -1938,32 +1842,32 @@
         <v>2</v>
       </c>
       <c r="I32">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B32:H32)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
         <v>40</v>
       </c>
-      <c r="G33">
-        <v>2</v>
+      <c r="H33">
+        <v>1</v>
       </c>
       <c r="I33">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B33:H33)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
         <v>41</v>
       </c>
-      <c r="G34">
-        <v>2</v>
+      <c r="H34">
+        <v>1</v>
       </c>
       <c r="I34">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B34:H34)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1973,12 +1877,9 @@
       <c r="G35">
         <v>1</v>
       </c>
-      <c r="H35">
-        <v>6</v>
-      </c>
       <c r="I35">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>SUM(B35:H35)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1989,56 +1890,53 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B36:H36)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>44</v>
       </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
       <c r="H37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B37:H37)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
         <v>45</v>
       </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38">
         <v>2</v>
       </c>
       <c r="I38">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B38:H38)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
         <v>46</v>
       </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
       <c r="H39">
         <v>2</v>
       </c>
       <c r="I39">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B39:H39)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2048,35 +1946,32 @@
       <c r="G40">
         <v>1</v>
       </c>
-      <c r="H40">
-        <v>1</v>
-      </c>
       <c r="I40">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B40:H40)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
         <v>48</v>
       </c>
-      <c r="G41">
-        <v>1</v>
+      <c r="H41">
+        <v>4</v>
       </c>
       <c r="I41">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B41:H41)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
         <v>49</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>1</v>
       </c>
       <c r="I42">
-        <f t="shared" si="0"/>
+        <f>SUM(B42:H42)</f>
         <v>1</v>
       </c>
     </row>
@@ -2084,11 +1979,11 @@
       <c r="A43" t="s">
         <v>50</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <f t="shared" si="0"/>
+        <f>SUM(B43:H43)</f>
         <v>1</v>
       </c>
     </row>
@@ -2099,9 +1994,12 @@
       <c r="G44">
         <v>1</v>
       </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
       <c r="I44">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B44:H44)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2109,34 +2007,34 @@
         <v>52</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B45:H45)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
         <v>53</v>
       </c>
-      <c r="G46">
-        <v>1</v>
+      <c r="H46">
+        <v>4</v>
       </c>
       <c r="I46">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B46:H46)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
         <v>54</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <f t="shared" si="0"/>
+        <f>SUM(B47:H47)</f>
         <v>1</v>
       </c>
     </row>
@@ -2144,36 +2042,45 @@
       <c r="A48" t="s">
         <v>55</v>
       </c>
-      <c r="G48">
-        <v>1</v>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
       </c>
       <c r="I48">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>SUM(B48:H48)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
         <v>56</v>
       </c>
-      <c r="H49">
-        <v>6</v>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
       </c>
       <c r="I49">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>SUM(B49:H49)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
         <v>57</v>
       </c>
-      <c r="H50">
-        <v>4</v>
+      <c r="G50">
+        <v>1</v>
       </c>
       <c r="I50">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B50:H50)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2181,11 +2088,11 @@
         <v>58</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>SUM(B51:H51)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2193,11 +2100,11 @@
         <v>59</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B52:H52)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2205,59 +2112,86 @@
         <v>60</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>SUM(B53:H53)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
         <v>61</v>
       </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
       <c r="H54">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I54">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B54:H54)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
         <v>62</v>
       </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
       <c r="H55">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B55:H55)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
         <v>63</v>
       </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56">
+        <v>4</v>
+      </c>
       <c r="H56">
         <v>2</v>
       </c>
       <c r="I56">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B56:H56)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
         <v>64</v>
       </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
       <c r="H57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I57">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B57:H57)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2265,11 +2199,11 @@
         <v>65</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B58:H58)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2277,11 +2211,11 @@
         <v>66</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B59:H59)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2292,7 +2226,7 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <f t="shared" si="0"/>
+        <f>SUM(B60:H60)</f>
         <v>2</v>
       </c>
     </row>
@@ -2300,12 +2234,15 @@
       <c r="A61" t="s">
         <v>68</v>
       </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
       <c r="H61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B61:H61)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2316,7 +2253,7 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <f t="shared" si="0"/>
+        <f>SUM(B62:H62)</f>
         <v>2</v>
       </c>
     </row>
@@ -2324,12 +2261,21 @@
       <c r="A63" t="s">
         <v>70</v>
       </c>
-      <c r="H63">
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+      <c r="G63">
         <v>2</v>
       </c>
       <c r="I63">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B63:H63)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2337,23 +2283,29 @@
         <v>71</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B64:H64)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
         <v>72</v>
       </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
       <c r="H65">
         <v>2</v>
       </c>
       <c r="I65">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>SUM(B65:H65)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2361,22 +2313,22 @@
         <v>73</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <f t="shared" ref="I66:I97" si="1">SUM(B66:H66)</f>
-        <v>1</v>
+        <f>SUM(B66:H66)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
         <v>74</v>
       </c>
-      <c r="H67">
+      <c r="G67">
         <v>1</v>
       </c>
       <c r="I67">
-        <f t="shared" si="1"/>
+        <f>SUM(B67:H67)</f>
         <v>1</v>
       </c>
     </row>
@@ -2384,12 +2336,15 @@
       <c r="A68" t="s">
         <v>75</v>
       </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
       <c r="H68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B68:H68)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2397,11 +2352,11 @@
         <v>76</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B69:H69)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2412,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <f t="shared" si="1"/>
+        <f>SUM(B70:H70)</f>
         <v>1</v>
       </c>
     </row>
@@ -2420,12 +2375,24 @@
       <c r="A71" t="s">
         <v>78</v>
       </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71">
+        <v>5</v>
+      </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B71:H71)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2436,7 +2403,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <f t="shared" si="1"/>
+        <f>SUM(B72:H72)</f>
         <v>1</v>
       </c>
     </row>
@@ -2448,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <f t="shared" si="1"/>
+        <f>SUM(B73:H73)</f>
         <v>1</v>
       </c>
     </row>
@@ -2456,35 +2423,47 @@
       <c r="A74" t="s">
         <v>81</v>
       </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>4</v>
+      </c>
       <c r="H74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B74:H74)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
         <v>82</v>
       </c>
-      <c r="H75">
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
         <v>1</v>
       </c>
       <c r="I75">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B75:H75)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
         <v>83</v>
       </c>
-      <c r="H76">
+      <c r="G76">
         <v>1</v>
       </c>
       <c r="I76">
-        <f t="shared" si="1"/>
+        <f>SUM(B76:H76)</f>
         <v>1</v>
       </c>
     </row>
@@ -2496,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <f t="shared" si="1"/>
+        <f>SUM(B77:H77)</f>
         <v>1</v>
       </c>
     </row>
@@ -2504,12 +2483,24 @@
       <c r="A78" t="s">
         <v>85</v>
       </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>3</v>
+      </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B78:H78)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2520,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <f t="shared" si="1"/>
+        <f>SUM(B79:H79)</f>
         <v>1</v>
       </c>
     </row>
@@ -2528,12 +2519,18 @@
       <c r="A80" t="s">
         <v>87</v>
       </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B80:H80)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2544,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <f t="shared" si="1"/>
+        <f>SUM(B81:H81)</f>
         <v>1</v>
       </c>
     </row>
@@ -2553,59 +2550,77 @@
         <v>89</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I82">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B82:H82)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
         <v>90</v>
       </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>3</v>
+      </c>
       <c r="H83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I83">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B83:H83)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
         <v>91</v>
       </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>3</v>
+      </c>
       <c r="H84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I84">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B84:H84)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
         <v>92</v>
       </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
       <c r="H85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I85">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B85:H85)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
         <v>93</v>
       </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B86:H86)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -2616,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <f t="shared" si="1"/>
+        <f>SUM(B87:H87)</f>
         <v>1</v>
       </c>
     </row>
@@ -2624,12 +2639,12 @@
       <c r="A88" t="s">
         <v>95</v>
       </c>
-      <c r="H88">
-        <v>1</v>
+      <c r="F88">
+        <v>2</v>
       </c>
       <c r="I88">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B88:H88)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -2640,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <f t="shared" si="1"/>
+        <f>SUM(B89:H89)</f>
         <v>1</v>
       </c>
     </row>
@@ -2652,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <f t="shared" si="1"/>
+        <f>SUM(B90:H90)</f>
         <v>1</v>
       </c>
     </row>
@@ -2660,24 +2675,39 @@
       <c r="A91" t="s">
         <v>98</v>
       </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
       <c r="H91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B91:H91)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
         <v>99</v>
       </c>
+      <c r="F92">
+        <v>5</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
       <c r="H92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I92">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B92:H92)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -2688,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <f t="shared" si="1"/>
+        <f>SUM(B93:H93)</f>
         <v>1</v>
       </c>
     </row>
@@ -2696,12 +2726,15 @@
       <c r="A94" t="s">
         <v>101</v>
       </c>
-      <c r="H94">
-        <v>1</v>
+      <c r="B94">
+        <v>5</v>
+      </c>
+      <c r="C94">
+        <v>4</v>
       </c>
       <c r="I94">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B94:H94)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -2712,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <f t="shared" si="1"/>
+        <f>SUM(B95:H95)</f>
         <v>1</v>
       </c>
     </row>
@@ -2720,12 +2753,18 @@
       <c r="A96" t="s">
         <v>103</v>
       </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
       <c r="H96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>SUM(B96:H96)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -2736,217 +2775,315 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <f t="shared" si="1"/>
+        <f>SUM(B97:H97)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>105</v>
+      </c>
+      <c r="H98">
+        <v>2</v>
+      </c>
+      <c r="I98">
+        <f>SUM(B98:H98)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>106</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <f>SUM(B99:H99)</f>
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>105</v>
-      </c>
-      <c r="B100">
-        <f t="shared" ref="B100:I100" si="2">SUM(B2:B97)</f>
-        <v>9</v>
-      </c>
-      <c r="C100">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="D100">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="E100">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="F100">
-        <f t="shared" si="2"/>
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="G100">
-        <f t="shared" si="2"/>
-        <v>72</v>
-      </c>
-      <c r="H100">
-        <f t="shared" si="2"/>
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="I100">
-        <f t="shared" si="2"/>
-        <v>288</v>
+        <f>SUM(B100:H100)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>108</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>3</v>
+      </c>
+      <c r="I101">
+        <f>SUM(B101:H101)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>109</v>
+      </c>
+      <c r="H102">
+        <v>2</v>
+      </c>
+      <c r="I102">
+        <f>SUM(B102:H102)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:9">
-      <c r="B103" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D103" s="1" t="s">
+      <c r="A103" t="s">
+        <v>110</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <f>SUM(B103:H103)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106">
+        <f t="shared" ref="B106:I106" si="0">SUM(B2:B103)</f>
+        <v>10</v>
+      </c>
+      <c r="C106">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="0"/>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="B109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9">
-      <c r="A104" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B104" t="s">
-        <v>107</v>
-      </c>
-      <c r="C104" t="s">
-        <v>108</v>
-      </c>
-      <c r="D104" t="s">
-        <v>109</v>
-      </c>
-      <c r="E104" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B105" t="s">
-        <v>107</v>
-      </c>
-      <c r="C105" t="s">
-        <v>108</v>
-      </c>
-      <c r="D105" t="s">
-        <v>112</v>
-      </c>
-      <c r="E105" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9">
-      <c r="A106" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B106" t="s">
-        <v>107</v>
-      </c>
-      <c r="C106" t="s">
-        <v>108</v>
-      </c>
-      <c r="D106" t="s">
-        <v>113</v>
-      </c>
-      <c r="E106" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9">
-      <c r="A107" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B107" t="s">
-        <v>108</v>
-      </c>
-      <c r="C107" t="s">
-        <v>107</v>
-      </c>
-      <c r="D107" t="s">
-        <v>117</v>
-      </c>
-      <c r="E107" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9">
-      <c r="A108" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B108" t="s">
-        <v>108</v>
-      </c>
-      <c r="C108" t="s">
-        <v>107</v>
-      </c>
-      <c r="D108" t="s">
-        <v>120</v>
-      </c>
-      <c r="E108" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
-      <c r="A109" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B109" t="s">
-        <v>108</v>
-      </c>
-      <c r="C109" t="s">
-        <v>122</v>
-      </c>
-      <c r="D109" t="s">
-        <v>109</v>
-      </c>
-      <c r="E109" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="1" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B110" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C110" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E110" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D111" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E111" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="1" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C112" t="s">
         <v>118</v>
       </c>
       <c r="D112" t="s">
+        <v>121</v>
+      </c>
+      <c r="E112" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B113" t="s">
+        <v>113</v>
+      </c>
+      <c r="C113" t="s">
+        <v>118</v>
+      </c>
+      <c r="D113" t="s">
+        <v>122</v>
+      </c>
+      <c r="E113" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E112" t="s">
-        <v>107</v>
+      <c r="B114" t="s">
+        <v>118</v>
+      </c>
+      <c r="C114" t="s">
+        <v>113</v>
+      </c>
+      <c r="D114" t="s">
+        <v>126</v>
+      </c>
+      <c r="E114" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B115" t="s">
+        <v>118</v>
+      </c>
+      <c r="C115" t="s">
+        <v>113</v>
+      </c>
+      <c r="D115" t="s">
+        <v>129</v>
+      </c>
+      <c r="E115" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B116" t="s">
+        <v>118</v>
+      </c>
+      <c r="C116" t="s">
+        <v>131</v>
+      </c>
+      <c r="D116" t="s">
+        <v>114</v>
+      </c>
+      <c r="E116" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B117" t="s">
+        <v>113</v>
+      </c>
+      <c r="C117" t="s">
+        <v>118</v>
+      </c>
+      <c r="D117" t="s">
+        <v>129</v>
+      </c>
+      <c r="E117" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B118" t="s">
+        <v>118</v>
+      </c>
+      <c r="C118" t="s">
+        <v>113</v>
+      </c>
+      <c r="D118" t="s">
+        <v>115</v>
+      </c>
+      <c r="E118" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B119" t="s">
+        <v>118</v>
+      </c>
+      <c r="C119" t="s">
+        <v>127</v>
+      </c>
+      <c r="D119" t="s">
+        <v>115</v>
+      </c>
+      <c r="E119" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A2:I97">
-    <sortCondition ref="B2" descending="1"/>
+    <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
